--- a/outputs/evaluation/decision/v2/CF_M08/run_1/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_1/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25</v>
+        <v>0.7143</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667</v>
+        <v>0.3571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8192</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.1333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.6667</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1667</v>
+        <v>0.3571</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,16 +974,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7936</v>
+        <v>0.772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1019,65 +1019,65 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering. [...] Next.js supports both Client-Side Rendering (CSR) and Server-Side Rendering (SSR), allowing the choice of the best strategy according to the application's needs.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>C_01, C_02</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_08, AU_04</t>
+          <t>AU_03, AU_06</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41, 44</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>*CF_M08_C15</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8448</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1088,59 +1088,312 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Data Service (PostgreSQL) provides the relational database for storing application data. [...] Prisma is an ORM tool used to simplify database access and management.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>AU_04, AU_07, AU_08</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>41, 42</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>*CF_M08_C23</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8321</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="L3" t="n">
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Traefik is a modern reverse proxy and load balancer designed to manage incoming and outgoing HTTP and HTTPS traffic. HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R_20, R_21, C_03</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, logs, or database connections, where having multiple instances could lead to inconsistent states or inefficient resource use.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C_04, Robustness</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>CF_M08_C06</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CF_M08_P05</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M08_AD01</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8379</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Security Service (Traefik) functions as a reverse proxy and load balancer, managing HTTP and HTTPS request routing. [...] Traefik acts as an intermediary for client requests to backend servers. It redirects incoming requests (from users) to the corresponding internal services. Load Balancer: Distributes traffic between multiple instances of a service, improving availability and responsiveness of the application.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C_04, C_08</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>AU_02, AU_05</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU22</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>41, 43</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9946</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C_05, Maintainability</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,12 +1455,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. The software architecture based on microservices is a design and software development approach where an application is built as a collection of small and independent services that communicate with each other.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. [...] The system must be scalable to handle an increase in the number of users and volume of data. [...] To adapt to future growth and ensure performance.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, R_29, C_07</t>
+          <t>C_07, Scalability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1217,191 +1470,51 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33, 41</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6383</v>
+        <v>0.6826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects, where a subject maintains a list of observers. [...] When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_18, C_02</t>
+          <t>C_06, Adaptability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_03, AU_06</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7467</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>In the case of this application, said services run on Amazon EC2 instances and are managed by Docker, which manages the execution of the containers.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C_04</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.648</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD09</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.7333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M08_AD07</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5961</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is generally used to manage shared resources, such as configurations, logs, or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.639</v>
+        <v>0.6024</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,17 +1571,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1485,29 +1599,28 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6879</v>
+        <v>0.7603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1519,7 +1632,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8248</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="4">
@@ -1548,27 +1661,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6244</v>
+        <v>0.5889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M08_C15</t>
+          <t>*CF_M08_C16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1585,23 +1698,23 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7467</v>
+        <v>0.6506999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AD06</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
+          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M08_C16</t>
+          <t>*CF_M08_C17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1610,64 +1723,64 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7212</v>
+        <v>0.7027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M08_C17</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.7033</v>
+        <v>0.6825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD08</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
+          <t>*CF_M08_C20, *CF_M08_C21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1680,60 +1793,60 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6878</v>
+        <v>0.7319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7333</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1750,40 +1863,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD11</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M08_C23</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.7723</v>
+        <v>0.7446</v>
       </c>
     </row>
   </sheetData>
